--- a/Result/profitability/4535.xlsx
+++ b/Result/profitability/4535.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4974999999999999</v>
+        <v>0.47375</v>
       </c>
       <c r="N2" t="n">
-        <v>20.7875</v>
+        <v>20.44125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.59375</v>
+        <v>0.54125</v>
       </c>
       <c r="N3" t="n">
-        <v>21.9375</v>
+        <v>21.60875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6625</v>
+        <v>0.62625</v>
       </c>
       <c r="N4" t="n">
-        <v>22.81875</v>
+        <v>22.35125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6487499999999999</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>22.68625</v>
+        <v>22.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.73375</v>
+        <v>0.7125</v>
       </c>
       <c r="N6" t="n">
-        <v>22.74375</v>
+        <v>22.465</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7575</v>
+        <v>0.74625</v>
       </c>
       <c r="N7" t="n">
-        <v>23.4425</v>
+        <v>23.135</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.80875</v>
       </c>
       <c r="N8" t="n">
-        <v>23.8875</v>
+        <v>23.82625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>667</v>
+      </c>
+      <c r="D75" t="n">
+        <v>553</v>
+      </c>
+      <c r="E75" t="n">
+        <v>115</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>57</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>66</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.23625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4899999999999984</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02776203966005653</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.416666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.289999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1177377892030848</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
